--- a/input/Reuniones.xlsx
+++ b/input/Reuniones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F43FB3-E3FF-4EB2-8CA2-5E3A756B3455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188DDEAF-0CC9-4D4C-A858-E237E391DCEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="165" windowWidth="20490" windowHeight="10740" xr2:uid="{A9D1B21C-5760-4724-943B-CEEE3084E290}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D1B21C-5760-4724-943B-CEEE3084E290}"/>
   </bookViews>
   <sheets>
     <sheet name="ProyectosCosta" sheetId="4" r:id="rId1"/>

--- a/input/Reuniones.xlsx
+++ b/input/Reuniones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\REUNIONES BQUILLA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8067B2B4-6F83-46CD-952D-32DB8008D697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2007A04D-C5DD-429C-8F5C-230FF7C5CAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D1B21C-5760-4724-943B-CEEE3084E290}"/>
   </bookViews>

--- a/input/Reuniones.xlsx
+++ b/input/Reuniones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\REUNIONES BQUILLA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2007A04D-C5DD-429C-8F5C-230FF7C5CAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7506AD87-FB89-4497-9B21-E83938711E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D1B21C-5760-4724-943B-CEEE3084E290}"/>
+    <workbookView xWindow="-18240" yWindow="2250" windowWidth="15375" windowHeight="7785" xr2:uid="{A9D1B21C-5760-4724-943B-CEEE3084E290}"/>
   </bookViews>
   <sheets>
     <sheet name="ProyectosBquilla" sheetId="4" r:id="rId1"/>

--- a/input/Reuniones.xlsx
+++ b/input/Reuniones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\REUNIONES BQUILLA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7506AD87-FB89-4497-9B21-E83938711E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83636A96-2B6B-4F0F-9C24-C81E17768524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18240" yWindow="2250" windowWidth="15375" windowHeight="7785" xr2:uid="{A9D1B21C-5760-4724-943B-CEEE3084E290}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A9D1B21C-5760-4724-943B-CEEE3084E290}"/>
   </bookViews>
   <sheets>
     <sheet name="ProyectosBquilla" sheetId="4" r:id="rId1"/>
